--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$360</definedName>

--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$360</definedName>

--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$360</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$336</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E360"/>
+  <dimension ref="A1:E336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GAR2SQ</t>
+          <t>AR2012</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -536,29 +536,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra kortfattat både muntligt och skriftligt för några av de mer betydelse…</t>
+          <t>11 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR2012</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AEN252</t>
+          <t>GAR2SQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33 ord: - kommunicera och argumentera i tal och skrift för sina egna tolkningar och krit…</t>
+          <t>26 ord: - redogöra kortfattat både muntligt och skriftligt för några av de mer betydelse…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GAR2SQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AEN299</t>
+          <t>AEN252</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33 ord: - i tal och skrift framföra och argumentera för sina egna tolkningar av, och kri…</t>
+          <t>33 ord: - kommunicera och argumentera i tal och skrift för sina egna tolkningar och krit…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN299</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN252</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AEN29A</t>
+          <t>AEN299</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,19 +622,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30 ord: - på en tydlig och korrekt akademisk engelska framföra och argumentera i tal och…</t>
+          <t>33 ord: - i tal och skrift framföra och argumentera för sina egna tolkningar av, och kri…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN299</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>AEN2BQ</t>
+          <t>AEN29A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
+          <t>30 ord: - på en tydlig och korrekt akademisk engelska framföra och argumentera i tal och…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN29A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AEN2BR</t>
+          <t>AEN2BQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AEN2BT</t>
+          <t>AEN2BW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AEN2BW</t>
+          <t>AEN2BZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för och kritiskt reflektera över politiska, kulturella och etiska frå…</t>
+          <t>27 ord: - självständigt analysera ett urval litterära verk från olika epoker som fokuser…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AEN2BZ</t>
+          <t>AEN2C2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27 ord: - självständigt analysera ett urval litterära verk från olika epoker som fokuser…</t>
+          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2BZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2C2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AEN2C2</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
+          <t>39 ord: - beskriva och förklara grundläggande språkliga strukturer och företeelser (t.ex…</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2C2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>39 ord: - beskriva och förklara grundläggande språkliga strukturer och företeelser (t.ex…</t>
+          <t>26 ord: - tillämpa sina kunskaper om, och förståelse av, det engelska språkets struktur …</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26 ord: - tillämpa sina kunskaper om, och förståelse av, det engelska språkets struktur …</t>
+          <t>30 ord: - identifiera grammatiska och stilistiska fel i en egenproducerad text, rätta de…</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30 ord: - identifiera grammatiska och stilistiska fel i en egenproducerad text, rätta de…</t>
+          <t>30 ord: - identifiera de vanligaste problemen som inlärare av engelska har samt beskriva…</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,19 +892,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30 ord: - identifiera de vanligaste problemen som inlärare av engelska har samt beskriva…</t>
+          <t>27 ord: - visa insikt i hur engelska används skriftligt på olika sätt i olika situatione…</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27 ord: - visa insikt i hur engelska används skriftligt på olika sätt i olika situatione…</t>
+          <t>26 ord: - visa fördjupad kunskap och förståelse om ett urval samtida litterära verk från…</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad kunskap och förståelse om ett urval samtida litterära verk från…</t>
+          <t>30 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av de li…</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av de li…</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN2034</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EN2034</t>
+          <t>EN2035</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EN2035</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
+          <t>25 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 12)</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
+          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,17 +1130,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
+          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>EN3062</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>31 ord: - föra en fördjupad kritisk diskussion kring begrepp som identitet, liminalitet …</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>31 ord: - föra en fördjupad kritisk diskussion kring begrepp som identitet, liminalitet …</t>
+          <t>33 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar och krit…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EN3062</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar och krit…</t>
+          <t>26 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>26 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>31 ord: - med högt ställda krav på språklig kommunikationsförmåga, skriftligt såväl som …</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31 ord: - med högt ställda krav på språklig kommunikationsförmåga, skriftligt såväl som …</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - visa förtrogenhet med aktuella forskningsfrågor, begrepp och teorier inom väst…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26 ord: - visa förtrogenhet med aktuella forskningsfrågor, begrepp och teorier inom väst…</t>
+          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
+          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
+          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
+          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
+          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
+          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN3072</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
+          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
+          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EN3072</t>
+          <t>EN3073</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
+          <t>27 ord: - kritiskt utvärdera språkvetenskapliga data som presenterats i tidigare forskni…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EN3073</t>
+          <t>EN3074</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt utvärdera språkvetenskapliga data som presenterats i tidigare forskni…</t>
+          <t>30 ord: - demonstrera kunskap om genreanalys med hänvisning till kommunikativa funktione…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30 ord: - demonstrera kunskap om genreanalys med hänvisning till kommunikativa funktione…</t>
+          <t>28 ord: - kommunicera idéer, utveckla argument och diskutera forskningsarbete på ett sät…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EN3074</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>28 ord: - kommunicera idéer, utveckla argument och diskutera forskningsarbete på ett sät…</t>
+          <t>26 ord: - visa på insikt om och fördjupad förståelse för de utvalda områdena inom tilläm…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>26 ord: - visa på insikt om och fördjupad förståelse för de utvalda områdena inom tilläm…</t>
+          <t>26 ord: - visa förståelse för och kritiskt granska centrala tillämpningar inom tillämpad…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26 ord: - visa förståelse för och kritiskt granska centrala tillämpningar inom tillämpad…</t>
+          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>EN3076</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
+          <t>38 ord: - kritiskt utvärdera engelskans roll i sammanhang som är relevanta för tillämpad…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>38 ord: - kritiskt utvärdera engelskans roll i sammanhang som är relevanta för tillämpad…</t>
+          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
+          <t>30 ord: - uppvisa en avancerad kunskap om ett av områdena inom tillämpad engelsk lingvis…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>30 ord: - uppvisa en avancerad kunskap om ett av områdena inom tillämpad engelsk lingvis…</t>
+          <t>28 ord: - visa förmåga att analysera, kritiskt bedöma och hantera komplexa företeelser o…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att analysera, kritiskt bedöma och hantera komplexa företeelser o…</t>
+          <t>26 ord: - visa på förmåga att utveckla en forskningsfråga med stöd från handledaren och …</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26 ord: - visa på förmåga att utveckla en forskningsfråga med stöd från handledaren och …</t>
+          <t>31 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12)</t>
+          <t>33 ord: - visa fördjupad förståelse för elevers syn på och upplevelser av sitt språklära…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>33 ord: - visa fördjupad förståelse för elevers syn på och upplevelser av sitt språklära…</t>
+          <t>29 ord: - redogöra för olika former av informations- och digitala hjälpmedel för att utv…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>GEN28Q</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,17 +2048,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för olika former av informations- och digitala hjälpmedel för att utv…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av litte…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>28 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av litte…</t>
+          <t>30 ord: - redogöra för hur olika former av digitala verktyg kan användas för att utveckl…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GEN28Q</t>
+          <t>GEN2BJ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>30 ord: - redogöra för hur olika former av digitala verktyg kan användas för att utveckl…</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - muntligt och skriftligt diskutera och motivera val av innehåll, material och a…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GEN2BJ</t>
+          <t>GEN2BK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt diskutera och motivera val av innehåll, material och a…</t>
+          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GEN2BK</t>
+          <t>GEN2LD</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 12)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GEN2LD</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GEN33R</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN33R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN37A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12)</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN37A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GEN37A</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,24 +2399,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - visa ett kritiskt förhållningssätt till olika typer av kulturella texter samt …</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GEN37A</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
+          <t>29 ord: - visa grundläggande kunskaper om ett urval centrala kulturella och litterära te…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GEN3C5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,24 +2453,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>28 ord: - visa ett kritiskt förhållningssätt till olika typer av kulturella texter samt …</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GEN3C5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>29 ord: - visa grundläggande kunskaper om ett urval centrala kulturella och litterära te…</t>
+          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GEN3C5</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GEN3C5</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,12 +2539,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - visa på färdigheter i att kritiskt reflektera, analysera och tolka litterära t…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>29 ord: - visa på färdigheter i att kritiskt reflektera, analysera och tolka litterära t…</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>30 ord: - visa fördjupade kunskaper om användning av IKT i språkundervisningen, IKT-utve…</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,24 +2777,24 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30 ord: - visa fördjupade kunskaper om användning av IKT i språkundervisningen, IKT-utve…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3E6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2939,24 +2939,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3E7</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GEN3E6</t>
+          <t>GEN3E7</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GEN3E7</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GEN3E7</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>31 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ENA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR27P</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
+          <t>28 ord: - utifrån egen eller befintlig sångöversättning tillämpa centrala perspektiv ino…</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>27 ord: - redogöra för de vanligaste problemen som svenska inlärare av franska har när d…</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>AFR27P</t>
+          <t>FR3022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,19 +3268,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån egen eller befintlig sångöversättning tillämpa centrala perspektiv ino…</t>
+          <t>41 ord: - utifrån en frågeställning självständigt söka, samla, kritiskt värdera samt tol…</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>FR3022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3295,19 +3295,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för de vanligaste problemen som svenska inlärare av franska har när d…</t>
+          <t>30 ord: - ta till sig konstruktiva synpunkter från såväl lärare som andra studenter och …</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FR3022</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3322,19 +3322,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>41 ord: - utifrån en frågeställning självständigt söka, samla, kritiskt värdera samt tol…</t>
+          <t>26 ord: - samla in relevant språkvetenskapligt eller litterärt material på franska för e…</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>FR3022</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3349,19 +3349,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>30 ord: - ta till sig konstruktiva synpunkter från såväl lärare som andra studenter och …</t>
+          <t>30 ord: - författa ett skriftligt teoretiskt arbete, på god franska där studenten använd…</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GFR27N</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3371,24 +3371,24 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3403,19 +3403,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>26 ord: - samla in relevant språkvetenskapligt eller litterärt material på franska för e…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>30 ord: - författa ett skriftligt teoretiskt arbete, på god franska där studenten använd…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>37 ord: - visa fördjupade kunskaper om användning av digitala verktyg i språkundervisnin…</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>32 ord: - visa förmåga att formulera en relevant forskningsfråga inom ett avgränsat prob…</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -3577,7 +3577,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3587,24 +3587,24 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3619,19 +3619,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>37 ord: - visa fördjupade kunskaper om användning av digitala verktyg i språkundervisnin…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att formulera en relevant forskningsfråga inom ett avgränsat prob…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3668,24 +3668,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3700,19 +3700,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3722,24 +3722,24 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>18 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>27 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR3CZ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3781,19 +3781,19 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>27 ord: - samla in relevant språkvetenskapligt, litterärt eller språkdidaktiskt material…</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3CZ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3803,24 +3803,24 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 12)</t>
+          <t>39 ord: - författa ett skriftligt teoretiskt arbete på god franska, där den studerande a…</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3830,24 +3830,24 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GFR3CZ</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3862,19 +3862,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>27 ord: - samla in relevant språkvetenskapligt, litterärt eller språkdidaktiskt material…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GFR3CZ</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>39 ord: - författa ett skriftligt teoretiskt arbete på god franska, där den studerande a…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>44 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4046,24 +4046,24 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4078,19 +4078,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>46 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4262,24 +4262,24 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>78 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4294,19 +4294,19 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>78 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4375,19 +4375,19 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4407,14 +4407,14 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4429,19 +4429,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4483,19 +4483,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4532,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>44 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4667,24 +4667,24 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4699,19 +4699,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>46 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -4873,88 +4873,88 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GIT2TL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4969,19 +4969,19 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4996,105 +4996,105 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GIT2TL</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>31 ord: - diskutera, ur ett teoretiskt och kritiskt grundat perspektiv, politiska, kultu…</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GJP39X</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 4)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>GJP3B2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
+          <t>26 ord: - analysera och översätta olika typer av dokument från japanska till engelska oc…</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5158,213 +5158,213 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>31 ord: - diskutera, ur ett teoretiskt och kritiskt grundat perspektiv, politiska, kultu…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen tolkning och förståelse av de lit…</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>AJP27A</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - med högt ställda krav på skriftlig och muntlig kommunikationsförmåga, presente…</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>AJP27B</t>
+          <t>AKI2BN</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - analysera och formulera välgrundade perspektiv på centrala frågor i det samtid…</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP27B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
+          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GJP23L</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - identifiera och förklara olika grammatiska svårigheter i det kinesiska språket…</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP23L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GJP39V</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - redogöra för vanliga svårigheter svensktalande inlärare upplever gällande kine…</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>GJP39X</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GJP3AY</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - visa kunskap om bakgrunden till skolans styrdokument med fokus på det europeis…</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3AY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GJP3B2</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5374,78 +5374,78 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och översätta olika typer av dokument från japanska till engelska oc…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>JP1045</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>JP1046</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP1046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen tolkning och förståelse av de lit…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>28 ord: - med högt ställda krav på skriftlig och muntlig kommunikationsförmåga, presente…</t>
+          <t>32 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>AKI2BN</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5504,24 +5504,24 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och formulera välgrundade perspektiv på centrala frågor i det samtid…</t>
+          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5531,24 +5531,24 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5558,29 +5558,29 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>28 ord: - identifiera och förklara olika grammatiska svårigheter i det kinesiska språket…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GPR256</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för vanliga svårigheter svensktalande inlärare upplever gällande kine…</t>
+          <t>28 ord: - inom given tidsram genomföra en självständig litteraturvetenskaplig eller språ…</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GPR2VP</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5617,24 +5617,24 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>26 ord: - kritiskt analysera och problematisera aktuella forskningsfrågor, begrepp, teor…</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GPR2XS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5644,24 +5644,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om bakgrunden till skolans styrdokument med fokus på det europeis…</t>
+          <t>27 ord: - visa förståelse för olika aspekter av portugisiskans ljudsystem som betonings-…</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5671,51 +5671,51 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>PR1017</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5725,24 +5725,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>28 ord: - visa insikt i det portugisiska språkets fonetik och fonologi genom att uttala …</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>PR1021</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5752,24 +5752,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GRY2BS</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5779,132 +5779,132 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>31 ord: - inom en given tidsram genomföra en självständig litteraturvetenskaplig, kultur…</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GKI2PZ</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>33 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GPR256</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5914,24 +5914,24 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>28 ord: - inom given tidsram genomföra en självständig litteraturvetenskaplig eller språ…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GPR2VP</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5941,51 +5941,51 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera och problematisera aktuella forskningsfrågor, begrepp, teor…</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>GPR2XS</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GPR2XS</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5995,24 +5995,24 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>27 ord: - visa förståelse för olika aspekter av portugisiskans ljudsystem som betonings-…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6022,78 +6022,78 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
+          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12)</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>PR1017</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>PR1017</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -6103,51 +6103,51 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>28 ord: - visa insikt i det portugisiska språkets fonetik och fonologi genom att uttala …</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>PR1021</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>38 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>PR1021</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -6157,24 +6157,24 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
+          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GRY2BS</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6184,19 +6184,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>31 ord: - inom en given tidsram genomföra en självständig litteraturvetenskaplig, kultur…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6211,19 +6211,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6233,24 +6233,24 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6260,24 +6260,24 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>33 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6346,19 +6346,19 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6373,19 +6373,19 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6395,29 +6395,29 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6454,24 +6454,24 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6535,105 +6535,105 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>38 lärandemål (maximum rekommenderat: 12)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
+          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6643,159 +6643,159 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6805,100 +6805,100 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6908,24 +6908,24 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6935,24 +6935,24 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6962,24 +6962,24 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6989,24 +6989,24 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7021,19 +7021,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7043,24 +7043,24 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7075,19 +7075,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7097,24 +7097,24 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12)</t>
+          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7124,24 +7124,24 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7151,24 +7151,24 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7178,24 +7178,24 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12)</t>
+          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7205,24 +7205,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12)</t>
+          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7237,19 +7237,19 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 12)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7259,24 +7259,24 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7291,78 +7291,78 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -7372,186 +7372,186 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GSS3C6</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>GSS3H9</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12)</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7561,24 +7561,24 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7588,78 +7588,78 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
+          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12)</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7669,24 +7669,24 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
+          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7723,78 +7723,78 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -7804,24 +7804,24 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -7831,19 +7831,19 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7858,19 +7858,19 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7885,19 +7885,19 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7907,24 +7907,24 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7934,24 +7934,24 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7961,24 +7961,24 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7993,19 +7993,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
+          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8015,24 +8015,24 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 12)</t>
+          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,19 +8047,19 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8074,19 +8074,19 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8096,24 +8096,24 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 12)</t>
+          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8177,24 +8177,24 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12)</t>
+          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
+          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8263,24 +8263,24 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8290,24 +8290,24 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8317,24 +8317,24 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8344,24 +8344,24 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8398,51 +8398,51 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
+          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8452,24 +8452,24 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8479,51 +8479,51 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12)</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8533,24 +8533,24 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8560,24 +8560,24 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -8587,24 +8587,24 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -8614,24 +8614,24 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8641,51 +8641,51 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8695,24 +8695,24 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -8722,24 +8722,24 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -8749,19 +8749,19 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8776,19 +8776,19 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8803,19 +8803,19 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8825,24 +8825,24 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12)</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8857,19 +8857,19 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8879,24 +8879,24 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GTY2SU</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8906,24 +8906,24 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8933,24 +8933,24 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GTY2SY</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8960,24 +8960,24 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8992,19 +8992,19 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9019,19 +9019,19 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9046,19 +9046,19 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9068,24 +9068,24 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>36 lärandemål (maximum rekommenderat: 12)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9095,24 +9095,24 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9127,19 +9127,19 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9154,19 +9154,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9181,19 +9181,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9208,19 +9208,19 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9262,19 +9262,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9289,19 +9289,19 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9311,24 +9311,24 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>34 lärandemål (maximum rekommenderat: 12)</t>
+          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9343,19 +9343,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9370,19 +9370,19 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9397,19 +9397,19 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9424,19 +9424,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9473,24 +9473,24 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9505,665 +9505,17 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>37 lärandemål (maximum rekommenderat: 12)</t>
-        </is>
-      </c>
-      <c r="E337" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
-        </is>
-      </c>
-      <c r="E338" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
-        </is>
-      </c>
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
-        </is>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
-        </is>
-      </c>
-      <c r="E341" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
-        </is>
-      </c>
-      <c r="E342" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
-        </is>
-      </c>
-      <c r="E343" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="2" t="inlineStr">
-        <is>
-          <t>GTY3J9</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
-        </is>
-      </c>
-      <c r="E344" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="2" t="inlineStr">
-        <is>
-          <t>GTY3JB</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>15 lärandemål (maximum rekommenderat: 12)</t>
-        </is>
-      </c>
-      <c r="E345" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" s="2" t="inlineStr">
-        <is>
-          <t>TY1049</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>För få mål</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>3 lärandemål (minimum rekommenderat: 4)</t>
-        </is>
-      </c>
-      <c r="E346" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="2" t="inlineStr">
-        <is>
-          <t>TY1066</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
-        </is>
-      </c>
-      <c r="E347" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="2" t="inlineStr">
-        <is>
-          <t>TY1066</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
-        </is>
-      </c>
-      <c r="E348" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>TY1066</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
-        </is>
-      </c>
-      <c r="E349" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="inlineStr">
-        <is>
-          <t>TY1069</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
-        </is>
-      </c>
-      <c r="E350" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>TY1071</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
-        </is>
-      </c>
-      <c r="E351" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>TY1073</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
-        </is>
-      </c>
-      <c r="E352" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>TY2007</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
-        </is>
-      </c>
-      <c r="E353" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>TY2007</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="2" t="inlineStr">
-        <is>
-          <t>TY2007</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
-        </is>
-      </c>
-      <c r="E355" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="2" t="inlineStr">
-        <is>
-          <t>TY2007</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
-        </is>
-      </c>
-      <c r="E356" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
-        </is>
-      </c>
-      <c r="E357" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
-        </is>
-      </c>
-      <c r="E358" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
-        </is>
-      </c>
-      <c r="E359" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E360"/>
+  <autoFilter ref="A1:E336"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -10835,54 +10187,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId668"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A336" r:id="rId669"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A337" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A338" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A339" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A340" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A341" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E341" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A342" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E342" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A343" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E343" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A344" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E344" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A345" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E345" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A346" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E346" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A347" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E347" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A348" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E348" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A349" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E349" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A350" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E350" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A351" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E351" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A352" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E352" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A353" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E353" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A354" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E354" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A355" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E355" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A356" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E356" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A357" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E357" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A358" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E358" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A359" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E359" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A360" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E360" r:id="rId718"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$336</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$340</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E336"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7357,7 +7357,7 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7367,24 +7367,24 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7394,24 +7394,24 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7426,19 +7426,19 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
+          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7453,19 +7453,19 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
+          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7480,19 +7480,19 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7502,24 +7502,24 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7534,19 +7534,19 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7556,24 +7556,24 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7583,24 +7583,24 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7615,19 +7615,19 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7637,24 +7637,24 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7664,24 +7664,24 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7696,19 +7696,19 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7723,19 +7723,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7750,19 +7750,19 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7777,19 +7777,19 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
+          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7804,19 +7804,19 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
@@ -7853,12 +7853,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
+          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7961,24 +7961,24 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7993,19 +7993,19 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
+          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8101,19 +8101,19 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
+          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
+          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
+          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
+          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,24 +8209,24 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
+          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
+          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8263,51 +8263,51 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8317,19 +8317,19 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8393,24 +8393,24 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8420,24 +8420,24 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8452,19 +8452,19 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8528,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8663,24 +8663,24 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8695,19 +8695,19 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8722,19 +8722,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
@@ -8771,12 +8771,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -8869,7 +8869,7 @@
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8879,24 +8879,24 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8911,19 +8911,19 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8938,19 +8938,19 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
@@ -8987,12 +8987,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9095,24 +9095,24 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9127,19 +9127,19 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9154,19 +9154,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9181,19 +9181,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9203,24 +9203,24 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9262,19 +9262,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9289,19 +9289,19 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
+          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9316,19 +9316,19 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
+          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9343,19 +9343,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9370,19 +9370,19 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
+          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9397,19 +9397,19 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
+          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9424,19 +9424,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9473,49 +9473,157 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>TY3013</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
         <is>
           <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
         </is>
       </c>
-      <c r="E336" s="2" t="inlineStr">
+      <c r="E340" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E336"/>
+  <autoFilter ref="A1:E340"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -10187,6 +10295,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E335" r:id="rId668"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A336" r:id="rId669"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A337" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A338" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A339" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A340" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId678"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$340</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$E$337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5818,7 +5818,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5828,17 +5828,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>33 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>33 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -6034,7 +6034,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6098,17 +6098,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>38 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
@@ -6125,12 +6125,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>38 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -6157,7 +6157,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6206,17 +6206,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
+          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6265,19 +6265,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6292,19 +6292,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
+          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6319,19 +6319,19 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6351,14 +6351,14 @@
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6368,51 +6368,51 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -6466,7 +6466,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6481,19 +6481,19 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6503,24 +6503,24 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6535,19 +6535,19 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6567,14 +6567,14 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6589,19 +6589,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6616,19 +6616,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6643,19 +6643,19 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6670,19 +6670,19 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6697,19 +6697,19 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6751,19 +6751,19 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6773,24 +6773,24 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6800,24 +6800,24 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6832,19 +6832,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6859,19 +6859,19 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6886,19 +6886,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6913,19 +6913,19 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6945,14 +6945,14 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6967,19 +6967,19 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6994,19 +6994,19 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7016,24 +7016,24 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7043,17 +7043,17 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
+          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
+          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
+          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
+          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
+          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7205,24 +7205,24 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7232,17 +7232,17 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -7291,19 +7291,19 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7323,14 +7323,14 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
+          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
+          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
+          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -7438,7 +7438,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7448,24 +7448,24 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
@@ -7502,12 +7502,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
+          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7556,17 +7556,17 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
@@ -7583,12 +7583,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -7627,7 +7627,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7637,17 +7637,17 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
@@ -7745,12 +7745,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7799,24 +7799,24 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
@@ -7853,12 +7853,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
+          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
+          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7988,24 +7988,24 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8020,19 +8020,19 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
+          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
@@ -8069,12 +8069,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8155,19 +8155,19 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
+          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8182,19 +8182,19 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8209,19 +8209,19 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
+          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8236,24 +8236,24 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
+          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8263,24 +8263,24 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
+          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8290,46 +8290,46 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>TYA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8344,19 +8344,19 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8371,19 +8371,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8393,24 +8393,24 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8425,19 +8425,19 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8447,24 +8447,24 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8479,19 +8479,19 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
@@ -8528,12 +8528,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -8614,7 +8614,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -8680,7 +8680,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8690,24 +8690,24 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8722,19 +8722,19 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
@@ -8771,12 +8771,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -8896,7 +8896,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8906,24 +8906,24 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8938,19 +8938,19 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
@@ -8987,12 +8987,12 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9122,24 +9122,24 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9154,19 +9154,19 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9181,19 +9181,19 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9203,24 +9203,24 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9235,19 +9235,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9262,19 +9262,19 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9289,19 +9289,19 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9316,19 +9316,19 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
+          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9343,19 +9343,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
+          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9370,12 +9370,12 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
+          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -9409,7 +9409,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9424,19 +9424,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
+          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9456,14 +9456,14 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9478,19 +9478,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
+          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9500,24 +9500,24 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY3016</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9532,98 +9532,17 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="2" t="inlineStr">
-        <is>
-          <t>TY2008</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
-        </is>
-      </c>
-      <c r="E338" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="2" t="inlineStr">
-        <is>
-          <t>TY3013</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>För många mål</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
-        </is>
-      </c>
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="2" t="inlineStr">
-        <is>
-          <t>TY3016</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>TYA</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
-        </is>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E340"/>
+  <autoFilter ref="A1:E337"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -10297,12 +10216,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E336" r:id="rId670"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A337" r:id="rId671"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E337" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A338" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E338" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A339" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E339" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A340" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E340" r:id="rId678"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$339</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G337"/>
+  <dimension ref="A1:G339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3806,50 +3806,50 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN3KC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>GEN3KC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3860,19 +3860,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
+          <t>30 ord: - redogöra för hur olika former av digitala verktyg kan användas för att utveckl…</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3893,19 +3893,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>31 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AFR27P</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3915,14 +3915,10 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -3930,19 +3926,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån egen eller befintlig sångöversättning tillämpa centrala perspektiv ino…</t>
+          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3952,7 +3948,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3963,19 +3959,19 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för de vanligaste problemen som svenska inlärare av franska har när d…</t>
+          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>FR3022</t>
+          <t>AFR27P</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3985,10 +3981,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2016-04-07</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -3996,19 +3996,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>41 ord: - utifrån en frågeställning självständigt söka, samla, kritiskt värdera samt tol…</t>
+          <t>28 ord: - utifrån egen eller befintlig sångöversättning tillämpa centrala perspektiv ino…</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>FR3022</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2016-04-07</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>30 ord: - ta till sig konstruktiva synpunkter från såväl lärare som andra studenter och …</t>
+          <t>27 ord: - redogöra för de vanligaste problemen som svenska inlärare av franska har när d…</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>FR3022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2016-04-07</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -4062,19 +4062,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>26 ord: - samla in relevant språkvetenskapligt eller litterärt material på franska för e…</t>
+          <t>41 ord: - utifrån en frågeställning självständigt söka, samla, kritiskt värdera samt tol…</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>FR3022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2016-04-07</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -4095,19 +4095,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>30 ord: - författa ett skriftligt teoretiskt arbete, på god franska där studenten använd…</t>
+          <t>30 ord: - ta till sig konstruktiva synpunkter från såväl lärare som andra studenter och …</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4117,30 +4117,30 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - samla in relevant språkvetenskapligt eller litterärt material på franska för e…</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -4161,12 +4161,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>30 ord: - författa ett skriftligt teoretiskt arbete, på god franska där studenten använd…</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4189,12 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>37 ord: - visa fördjupade kunskaper om användning av digitala verktyg i språkundervisnin…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att formulera en relevant forskningsfråga inom ett avgränsat prob…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4381,30 +4381,30 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>37 ord: - visa fördjupade kunskaper om användning av digitala verktyg i språkundervisnin…</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -4425,19 +4425,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>32 ord: - visa förmåga att formulera en relevant forskningsfråga inom ett avgränsat prob…</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4447,30 +4447,30 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4546,30 +4546,30 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4590,19 +4590,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GFR3CZ</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4612,30 +4612,30 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>27 ord: - samla in relevant språkvetenskapligt, litterärt eller språkdidaktiskt material…</t>
+          <t>18 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GFR3CZ</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -4656,19 +4656,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>39 ord: - författa ett skriftligt teoretiskt arbete på god franska, där den studerande a…</t>
+          <t>27 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3CZ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4684,24 +4684,24 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - samla in relevant språkvetenskapligt, litterärt eller språkdidaktiskt material…</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3CZ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4722,12 +4722,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>39 ord: - författa ett skriftligt teoretiskt arbete på god franska, där den studerande a…</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
       </c>
     </row>
@@ -4750,12 +4750,12 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -4932,7 +4932,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4948,24 +4948,24 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5206,30 +5206,30 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>78 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -5250,12 +5250,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>78 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -5349,19 +5349,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5443,24 +5443,24 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5707,24 +5707,24 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
@@ -5773,12 +5773,12 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -5955,81 +5955,73 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GIT2TL</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6059,14 +6051,14 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6096,14 +6088,14 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GIT2TL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6113,7 +6105,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -6133,80 +6125,88 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
+          <t>2021-12-21</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>31 ord: - diskutera, ur ett teoretiskt och kritiskt grundat perspektiv, politiska, kultu…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2020-01-29</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -6227,19 +6227,19 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
+          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>GJP39X</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6249,30 +6249,30 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>31 ord: - diskutera, ur ett teoretiskt och kritiskt grundat perspektiv, politiska, kultu…</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>GJP3B2</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -6293,19 +6293,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och översätta olika typer av dokument från japanska till engelska oc…</t>
+          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>GJP39X</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6315,40 +6315,40 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen tolkning och förståelse av de lit…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GJP3B2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -6359,29 +6359,29 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>28 ord: - med högt ställda krav på skriftlig och muntlig kommunikationsförmåga, presente…</t>
+          <t>26 ord: - analysera och översätta olika typer av dokument från japanska till engelska oc…</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>AKI2BN</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -6392,19 +6392,19 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och formulera välgrundade perspektiv på centrala frågor i det samtid…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen tolkning och förståelse av de lit…</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6414,30 +6414,30 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - med högt ställda krav på skriftlig och muntlig kommunikationsförmåga, presente…</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>AKI2BN</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>28 ord: - identifiera och förklara olika grammatiska svårigheter i det kinesiska språket…</t>
+          <t>26 ord: - analysera och formulera välgrundade perspektiv på centrala frågor i det samtid…</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
         </is>
       </c>
     </row>
@@ -6486,12 +6486,12 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för vanliga svårigheter svensktalande inlärare upplever gällande kine…</t>
+          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>28 ord: - identifiera och förklara olika grammatiska svårigheter i det kinesiska språket…</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om bakgrunden till skolans styrdokument med fokus på det europeis…</t>
+          <t>26 ord: - redogöra för vanliga svårigheter svensktalande inlärare upplever gällande kine…</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>28 ord: - visa kunskap om bakgrunden till skolans styrdokument med fokus på det europeis…</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6744,30 +6744,30 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -6788,19 +6788,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>32 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -6821,29 +6821,29 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GPR256</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2018-10-10</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -6854,52 +6854,52 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>28 ord: - inom given tidsram genomföra en självständig litteraturvetenskaplig eller språ…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GPR2VP</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2022-03-04</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera och problematisera aktuella forskningsfrågor, begrepp, teor…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPR2XS</t>
+          <t>GPR256</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -6920,19 +6920,19 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>27 ord: - visa förståelse för olika aspekter av portugisiskans ljudsystem som betonings-…</t>
+          <t>28 ord: - inom given tidsram genomföra en självständig litteraturvetenskaplig eller språ…</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GPR2VP</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2022-03-04</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -6953,19 +6953,19 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
+          <t>26 ord: - kritiskt analysera och problematisera aktuella forskningsfrågor, begrepp, teor…</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GPR2XS</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6975,30 +6975,30 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - visa förståelse för olika aspekter av portugisiskans ljudsystem som betonings-…</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>PR1017</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7008,14 +7008,10 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2012-09-13</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7023,19 +7019,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>28 ord: - visa insikt i det portugisiska språkets fonetik och fonologi genom att uttala …</t>
+          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>PR1021</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7045,47 +7041,47 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>GRY2BS</t>
+          <t>PR1017</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>2012-09-13</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7093,32 +7089,36 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>31 ord: - inom en given tidsram genomföra en självständig litteraturvetenskaplig, kultur…</t>
+          <t>28 ord: - visa insikt i det portugisiska språkets fonetik och fonologi genom att uttala …</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>PR1021</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2019-03-13</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>2014-09-11</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7126,56 +7126,52 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GRY2BS</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
+          <t>2019-10-09</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>33 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - inom en given tidsram genomföra en självständig litteraturvetenskaplig, kultur…</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7185,14 +7181,10 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
+          <t>2019-03-13</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7200,12 +7192,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
@@ -7232,12 +7224,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -7274,7 +7266,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -7311,7 +7303,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -7348,7 +7340,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -7385,7 +7377,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -7422,7 +7414,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -7434,7 +7426,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7444,10 +7436,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7455,19 +7451,19 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7477,10 +7473,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7488,19 +7488,19 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7510,30 +7510,30 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>38 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
@@ -7582,12 +7582,12 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>38 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
+          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -7632,7 +7632,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7642,34 +7642,30 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7679,14 +7675,10 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7694,19 +7686,19 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7716,30 +7708,34 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
+          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7749,10 +7745,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7760,19 +7760,19 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -7793,19 +7793,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7826,19 +7826,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7854,34 +7854,34 @@
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -7892,52 +7892,52 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7958,19 +7958,19 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -7991,19 +7991,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -8013,30 +8013,30 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -8046,30 +8046,30 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -8090,19 +8090,19 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -8123,19 +8123,19 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -8156,19 +8156,19 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -8189,19 +8189,19 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -8222,19 +8222,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -8255,19 +8255,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -8288,19 +8288,19 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
@@ -8321,19 +8321,19 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8343,30 +8343,30 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -8387,19 +8387,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8409,30 +8409,30 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -8453,19 +8453,19 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -8486,19 +8486,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -8524,14 +8524,14 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -8552,19 +8552,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -8585,19 +8585,19 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -8623,14 +8623,14 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8640,30 +8640,30 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -8684,19 +8684,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -8717,12 +8717,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
+          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
@@ -8745,12 +8745,12 @@
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
+          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -8772,14 +8772,10 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -8787,19 +8783,19 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
+          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -8809,14 +8805,10 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -8824,12 +8816,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
+          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8853,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
+          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -8873,7 +8865,7 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -8886,27 +8878,31 @@
           <t>2013-02-04</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8916,10 +8912,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -8927,19 +8927,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
+          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8949,40 +8949,40 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -8993,29 +8993,29 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -9026,19 +9026,19 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -9059,19 +9059,19 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
@@ -9092,19 +9092,19 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9125,19 +9125,19 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
+          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -9158,19 +9158,19 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
+          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9180,30 +9180,30 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -9213,30 +9213,30 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -9252,17 +9252,17 @@
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
@@ -9285,12 +9285,12 @@
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -9302,7 +9302,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -9318,24 +9318,24 @@
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -9356,12 +9356,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
@@ -9384,12 +9384,12 @@
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9417,24 +9417,24 @@
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9455,12 +9455,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -9500,7 +9500,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9510,30 +9510,30 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -9554,12 +9554,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
@@ -9582,12 +9582,12 @@
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9615,24 +9615,24 @@
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
+          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
+          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -9830,7 +9830,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9846,24 +9846,24 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
@@ -9912,12 +9912,12 @@
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
+          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -10016,19 +10016,19 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
+          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -10049,19 +10049,19 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
+          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -10082,19 +10082,19 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
+          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -10115,12 +10115,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
+          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
+          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -10160,17 +10160,17 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -10181,29 +10181,29 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
+          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -10214,19 +10214,19 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -10236,30 +10236,30 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -10285,14 +10285,14 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -10302,30 +10302,30 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -10346,12 +10346,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -10401,30 +10401,30 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -10445,12 +10445,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
@@ -10473,12 +10473,12 @@
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
@@ -10610,7 +10610,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
@@ -10688,7 +10688,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -10704,24 +10704,24 @@
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10742,12 +10742,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
@@ -10770,12 +10770,12 @@
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10962,30 +10962,30 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
@@ -11034,12 +11034,12 @@
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -11232,24 +11232,24 @@
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -11259,14 +11259,10 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11274,19 +11270,19 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -11296,27 +11292,23 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11340,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
@@ -11360,7 +11352,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -11370,10 +11362,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11381,19 +11377,19 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -11403,10 +11399,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr"/>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11414,19 +11414,19 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
+          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
+          <t>2016-02-11</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -11447,19 +11447,19 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
+          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -11469,14 +11469,10 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11484,19 +11480,19 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
+          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -11506,14 +11502,10 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11521,12 +11513,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
+          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
@@ -11558,7 +11550,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
@@ -11595,7 +11587,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
+          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
@@ -11607,7 +11599,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -11632,19 +11624,19 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11669,12 +11661,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11698,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
+          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
@@ -11718,7 +11710,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11728,69 +11720,143 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>TY3013</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B339" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
+      <c r="C339" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D339" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr">
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
         <is>
           <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
         </is>
       </c>
-      <c r="G337" s="2" t="inlineStr">
+      <c r="G339" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G337"/>
+  <autoFilter ref="A1:G339"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -12464,6 +12530,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G336" r:id="rId670"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A337" r:id="rId671"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G337" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A338" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A339" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId676"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$363</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G339"/>
+  <dimension ref="A1:G363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -855,7 +855,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EN1086</t>
+          <t>AEN2CU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,14 +865,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2012-02-16</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -880,12 +876,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>39 ord: - beskriva och förklara grundläggande språkliga strukturer och företeelser (t.ex…</t>
+          <t>26 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN2CU</t>
         </is>
       </c>
     </row>
@@ -917,7 +913,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>26 ord: - tillämpa sina kunskaper om, och förståelse av, det engelska språkets struktur …</t>
+          <t>39 ord: - beskriva och förklara grundläggande språkliga strukturer och företeelser (t.ex…</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -954,7 +950,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30 ord: - identifiera grammatiska och stilistiska fel i en egenproducerad text, rätta de…</t>
+          <t>26 ord: - tillämpa sina kunskaper om, och förståelse av, det engelska språkets struktur …</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -991,7 +987,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30 ord: - identifiera de vanligaste problemen som inlärare av engelska har samt beskriva…</t>
+          <t>30 ord: - identifiera grammatiska och stilistiska fel i en egenproducerad text, rätta de…</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1003,7 +999,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EN1129</t>
+          <t>EN1086</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1013,10 +1009,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2015-10-09</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>2012-02-16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -1024,19 +1024,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27 ord: - visa insikt i hur engelska används skriftligt på olika sätt i olika situatione…</t>
+          <t>30 ord: - identifiera de vanligaste problemen som inlärare av engelska har samt beskriva…</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1086</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>EN2025</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1046,14 +1046,10 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2016-05-26</t>
-        </is>
-      </c>
+          <t>2015-10-09</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -1061,12 +1057,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad kunskap och förståelse om ett urval samtida litterära verk från…</t>
+          <t>27 ord: - visa insikt i hur engelska används skriftligt på olika sätt i olika situatione…</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1094,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av de li…</t>
+          <t>26 ord: - visa fördjupad kunskap och förståelse om ett urval samtida litterära verk från…</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1110,7 +1106,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EN2028</t>
+          <t>EN2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1125,7 +1121,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2016-05-26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1135,19 +1131,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>30 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av de li…</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2025</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>EN2034</t>
+          <t>EN2028</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1157,10 +1153,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2013-06-14</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -1168,19 +1168,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2028</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>EN2035</t>
+          <t>EN2034</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1190,14 +1190,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2014-01-28</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2013-06-14</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -1205,19 +1201,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
+          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2034</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>EN2043</t>
+          <t>EN2035</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1227,23 +1223,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>2014-01-28</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2035</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
+          <t>25 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EN2046</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,23 +1326,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EN2047</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1403,19 +1403,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>35 ord: - resonera kring hur man tolkar språkvetenskapliga resultat, vilket inbegriper h…</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EN3062</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,14 +1425,10 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2013-09-03</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -1440,12 +1436,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>31 ord: - föra en fördjupad kritisk diskussion kring begrepp som identitet, liminalitet …</t>
+          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1473,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>33 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar och krit…</t>
+          <t>31 ord: - föra en fördjupad kritisk diskussion kring begrepp som identitet, liminalitet …</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1489,7 +1485,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>EN3063</t>
+          <t>EN3062</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1499,12 +1495,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2013-11-14</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1514,12 +1510,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>26 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>33 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar och krit…</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3062</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1547,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>31 ord: - med högt ställda krav på språklig kommunikationsförmåga, skriftligt såväl som …</t>
+          <t>26 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1563,7 +1559,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>EN3064</t>
+          <t>EN3063</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1573,27 +1569,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2013-12-09</t>
+          <t>2013-11-14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2015-11-03</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>31 ord: - med högt ställda krav på språklig kommunikationsförmåga, skriftligt såväl som …</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3063</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1616,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>26 ord: - visa förtrogenhet med aktuella forskningsfrågor, begrepp och teorier inom väst…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1637,7 +1633,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EN3070</t>
+          <t>EN3064</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1647,10 +1643,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2015-03-12</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>2013-12-09</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2015-11-03</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
+          <t>26 ord: - visa förtrogenhet med aktuella forskningsfrågor, begrepp och teorier inom väst…</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3064</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>EN3071</t>
+          <t>EN3070</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1719,17 +1719,17 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3070</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
+          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
+          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
+          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>EN3072</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1911,14 +1911,10 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2017-03-13</t>
-        </is>
-      </c>
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -1926,12 +1922,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
+          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1959,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
+          <t>27 ord: - diskutera olika sätt på vilka situationella faktorer kan påverka diskursen och…</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2000,7 +1996,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
+          <t>31 ord: - identifiera vilka de karakteristiska egenskaperna är hos olika typer av text, …</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2012,7 +2008,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EN3073</t>
+          <t>EN3072</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2022,10 +2018,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>2017-03-13</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -2033,19 +2033,19 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>27 ord: - kritiskt utvärdera språkvetenskapliga data som presenterats i tidigare forskni…</t>
+          <t>28 ord: - genomföra ett begränsat forskningsprojekt baserat på en liten samling med aute…</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3072</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>EN3074</t>
+          <t>EN3073</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>30 ord: - demonstrera kunskap om genreanalys med hänvisning till kommunikativa funktione…</t>
+          <t>27 ord: - kritiskt utvärdera språkvetenskapliga data som presenterats i tidigare forskni…</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3073</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>28 ord: - kommunicera idéer, utveckla argument och diskutera forskningsarbete på ett sät…</t>
+          <t>30 ord: - demonstrera kunskap om genreanalys med hänvisning till kommunikativa funktione…</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EN3075</t>
+          <t>EN3074</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>26 ord: - visa på insikt om och fördjupad förståelse för de utvalda områdena inom tilläm…</t>
+          <t>28 ord: - kommunicera idéer, utveckla argument och diskutera forskningsarbete på ett sät…</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3074</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>26 ord: - visa förståelse för och kritiskt granska centrala tillämpningar inom tillämpad…</t>
+          <t>26 ord: - visa på insikt om och fördjupad förståelse för de utvalda områdena inom tilläm…</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
+          <t>26 ord: - visa förståelse för och kritiskt granska centrala tillämpningar inom tillämpad…</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>EN3076</t>
+          <t>EN3075</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>38 ord: - kritiskt utvärdera engelskans roll i sammanhang som är relevanta för tillämpad…</t>
+          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3075</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
+          <t>38 ord: - kritiskt utvärdera engelskans roll i sammanhang som är relevanta för tillämpad…</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EN3077</t>
+          <t>EN3076</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>30 ord: - uppvisa en avancerad kunskap om ett av områdena inom tillämpad engelsk lingvis…</t>
+          <t>29 ord: - kommunicera idéer, utveckla argument och diskutera vetenskapliga arbeten på et…</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3076</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>28 ord: - visa förmåga att analysera, kritiskt bedöma och hantera komplexa företeelser o…</t>
+          <t>30 ord: - uppvisa en avancerad kunskap om ett av områdena inom tillämpad engelsk lingvis…</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>26 ord: - visa på förmåga att utveckla en forskningsfråga med stöd från handledaren och …</t>
+          <t>28 ord: - visa förmåga att analysera, kritiskt bedöma och hantera komplexa företeelser o…</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GEN222</t>
+          <t>EN3077</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2385,23 +2385,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2018-03-22</t>
+          <t>2017-03-13</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>26 ord: - visa på förmåga att utveckla en forskningsfråga med stöd från handledaren och …</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3077</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2424,12 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>33 ord: - visa fördjupad förståelse för elevers syn på och upplevelser av sitt språklära…</t>
+          <t>31 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>29 ord: - redogöra för olika former av informations- och digitala hjälpmedel för att utv…</t>
+          <t>33 ord: - visa fördjupad förståelse för elevers syn på och upplevelser av sitt språklära…</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GEN28Q</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2484,27 +2484,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2019-03-21</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
+          <t>2018-03-22</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>29 ord: - redogöra för olika former av informations- och digitala hjälpmedel för att utv…</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2527,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>28 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av litte…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2573,7 +2569,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>30 ord: - redogöra för hur olika former av digitala verktyg kan användas för att utveckl…</t>
+          <t>28 ord: - i skrift och tal kommunicera och argumentera för sina egna tolkningar av litte…</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2585,7 +2581,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GEN2BJ</t>
+          <t>GEN28Q</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2595,23 +2591,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2019-09-20</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>2019-03-21</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>30 ord: - redogöra för hur olika former av digitala verktyg kan användas för att utveckl…</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt diskutera och motivera val av innehåll, material och a…</t>
+          <t>19 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GEN2BK</t>
+          <t>GEN2BJ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2667,24 +2667,24 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>28 ord: - muntligt och skriftligt diskutera och motivera val av innehåll, material och a…</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GEN2LD</t>
+          <t>GEN2BK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2020-12-23</t>
+          <t>2019-09-20</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2705,19 +2705,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>17 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GEN2VE</t>
+          <t>GEN2LD</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2727,23 +2727,23 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2022-03-03</t>
+          <t>2020-12-23</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>14 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2766,12 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GEN379</t>
+          <t>GEN2VE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2VE</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2832,12 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GEN37A</t>
+          <t>GEN379</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2865,17 +2865,17 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
       </c>
     </row>
@@ -2898,12 +2898,12 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GEN3BR</t>
+          <t>GEN37A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>28 ord: - visa ett kritiskt förhållningssätt till olika typer av kulturella texter samt …</t>
+          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>29 ord: - visa grundläggande kunskaper om ett urval centrala kulturella och litterära te…</t>
+          <t>28 ord: - visa ett kritiskt förhållningssätt till olika typer av kulturella texter samt …</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GEN3C5</t>
+          <t>GEN3BR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2991,23 +2991,23 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
+          <t>29 ord: - visa grundläggande kunskaper om ett urval centrala kulturella och litterära te…</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3BR</t>
         </is>
       </c>
     </row>
@@ -3030,12 +3030,12 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 12 hp)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>GEN3CM</t>
+          <t>GEN3C5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3057,23 +3057,23 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>33 ord: - analysera litteratur från den engelskspråkiga världen med hjälp av relevant li…</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3C5</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3096,12 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>26 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>29 ord: - visa på färdigheter i att kritiskt reflektera, analysera och tolka litterära t…</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>29 ord: - visa på färdigheter i att kritiskt reflektera, analysera och tolka litterära t…</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>30 ord: - visa fördjupade kunskaper om användning av IKT i språkundervisningen, IKT-utve…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>30 ord: - visa fördjupade kunskaper om användning av IKT i språkundervisningen, IKT-utve…</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GEN3DG</t>
+          <t>GEN3CM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3387,23 +3387,23 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GEN3DK</t>
+          <t>GEN3DG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3525,17 +3525,17 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
       </c>
     </row>
@@ -3558,12 +3558,12 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -3575,7 +3575,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GEN3E6</t>
+          <t>GEN3DK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3596,19 +3596,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>27 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GEN3E7</t>
+          <t>GEN3E6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E6</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GEN3K3</t>
+          <t>GEN3E7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3684,23 +3684,23 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3E7</t>
         </is>
       </c>
     </row>
@@ -3723,12 +3723,12 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
+          <t>14 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
+          <t>28 ord: - förklara grundläggande typer av variation i det engelska språket, genom hänvis…</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
+          <t>28 ord: - redogöra för huvuddragen i de litterära och idéhistoriska epokerna inom den an…</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -3806,7 +3806,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GEN3KC</t>
+          <t>GEN3K3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3816,23 +3816,23 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen såväl som andras tolkning av hist…</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
       </c>
     </row>
@@ -3855,12 +3855,12 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>30 ord: - redogöra för hur olika former av digitala verktyg kan användas för att utveckl…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -3872,17 +3872,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN3KC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3893,19 +3893,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>31 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
+          <t>30 ord: - redogöra för hur olika former av digitala verktyg kan användas för att utveckl…</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
+          <t>31 ord: - visa förmåga att, med högt ställda krav på skriftlig och muntlig kommunikation…</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>32 ord: - visa fördjupad förmåga att, med högt ställda krav på skriftlig och muntlig kom…</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -3971,7 +3971,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>AFR27P</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3981,14 +3981,10 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2021-12-22</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -3996,19 +3992,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån egen eller befintlig sångöversättning tillämpa centrala perspektiv ino…</t>
+          <t>26 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>AFR27P</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4018,10 +4014,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
+          <t>2021-12-22</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>27 ord: - redogöra för de vanligaste problemen som svenska inlärare av franska har när d…</t>
+          <t>28 ord: - utifrån egen eller befintlig sångöversättning tillämpa centrala perspektiv ino…</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR27P</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>FR3022</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2016-04-07</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>41 ord: - utifrån en frågeställning självständigt söka, samla, kritiskt värdera samt tol…</t>
+          <t>27 ord: - redogöra för de vanligaste problemen som svenska inlärare av franska har när d…</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>30 ord: - ta till sig konstruktiva synpunkter från såväl lärare som andra studenter och …</t>
+          <t>41 ord: - utifrån en frågeställning självständigt söka, samla, kritiskt värdera samt tol…</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GFR2KR</t>
+          <t>FR3022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2016-04-07</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>26 ord: - samla in relevant språkvetenskapligt eller litterärt material på franska för e…</t>
+          <t>30 ord: - ta till sig konstruktiva synpunkter från såväl lärare som andra studenter och …</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FR3022</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>30 ord: - författa ett skriftligt teoretiskt arbete, på god franska där studenten använd…</t>
+          <t>26 ord: - samla in relevant språkvetenskapligt eller litterärt material på franska för e…</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2KR</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4183,23 +4183,23 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - författa ett skriftligt teoretiskt arbete, på god franska där studenten använd…</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2KR</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>37 ord: - visa fördjupade kunskaper om användning av digitala verktyg i språkundervisnin…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att formulera en relevant forskningsfråga inom ett avgränsat prob…</t>
+          <t>37 ord: - visa fördjupade kunskaper om användning av digitala verktyg i språkundervisnin…</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4447,23 +4447,23 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - visa förmåga att formulera en relevant forskningsfråga inom ett avgränsat prob…</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>32 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GFR2YU</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR2YU</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4612,23 +4612,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>18 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2YU</t>
         </is>
       </c>
     </row>
@@ -4651,12 +4651,12 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>27 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>18 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GFR3CZ</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4689,12 +4689,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>27 ord: - samla in relevant språkvetenskapligt, litterärt eller språkdidaktiskt material…</t>
+          <t>27 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>39 ord: - författa ett skriftligt teoretiskt arbete på god franska, där den studerande a…</t>
+          <t>27 ord: - samla in relevant språkvetenskapligt, litterärt eller språkdidaktiskt material…</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3CZ</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4750,17 +4750,17 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>39 ord: - författa ett skriftligt teoretiskt arbete på god franska, där den studerande a…</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CZ</t>
         </is>
       </c>
     </row>
@@ -4783,12 +4783,12 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5014,17 +5014,17 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
@@ -5047,12 +5047,12 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5272,23 +5272,23 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>78 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5311,12 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>78 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -5394,7 +5394,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GFR3HL</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -5415,12 +5415,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>26 ord: - visa förmåga att i skriftlig och muntlig form presentera och argumentera för e…</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -5493,7 +5493,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3HL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5509,17 +5509,17 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HL</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>44 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5773,17 +5773,17 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
@@ -5806,12 +5806,12 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>46 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
+          <t>29 ord: - självständigt välja relevant innehåll och arbetssätt i planeringen av språkund…</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>32 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen och den d…</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -6021,44 +6021,40 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>GIT2TG</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2021-12-21</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GIT2TK</t>
+          <t>GIT2TG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6088,14 +6084,14 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TG</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>GIT2TL</t>
+          <t>GIT2TK</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6125,14 +6121,14 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TK</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>GIT2TP</t>
+          <t>GIT2TL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6162,14 +6158,14 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TL</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y8</t>
+          <t>GIT2TP</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6179,7 +6175,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2021-12-21</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -6199,47 +6195,51 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2TP</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>AJP23P</t>
+          <t>GIT2Y8</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JAA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2020-01-29</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
+          <t>2 lärandemål (minimum rekommenderat: 3 för 7.5 hp)</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y8</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>AJP26Z</t>
+          <t>AJP23P</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2020-01-29</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -6260,19 +6260,19 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>31 ord: - diskutera, ur ett teoretiskt och kritiskt grundat perspektiv, politiska, kultu…</t>
+          <t>29 ord: - diskutera komponenter inom den litteraturvetenskapliga forskningsprocessen, fr…</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP23P</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>AJP2A9</t>
+          <t>AJP26Z</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -6293,19 +6293,19 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
+          <t>31 ord: - diskutera, ur ett teoretiskt och kritiskt grundat perspektiv, politiska, kultu…</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP26Z</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>GJP39X</t>
+          <t>AJP2A9</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6315,30 +6315,30 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>28 ord: - med hög språklig kommunikationsförmåga, skriftligt såväl som muntligt presente…</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AJP2A9</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GJP3B2</t>
+          <t>GJP39X</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6348,30 +6348,30 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2023-12-20</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och översätta olika typer av dokument från japanska till engelska oc…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP39X</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>JP2013</t>
+          <t>GJP3B2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -6392,29 +6392,29 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>28 ord: - muntligt och skriftligt kommunicera sin egen tolkning och förståelse av de lit…</t>
+          <t>26 ord: - analysera och översätta olika typer av dokument från japanska till engelska oc…</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GJP3B2</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>JP2013</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>JAA</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
+          <t>2016-04-15</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -6425,19 +6425,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>28 ord: - med högt ställda krav på skriftlig och muntlig kommunikationsförmåga, presente…</t>
+          <t>28 ord: - muntligt och skriftligt kommunicera sin egen tolkning och förståelse av de lit…</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=JP2013</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AKI2BN</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -6458,19 +6458,19 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och formulera välgrundade perspektiv på centrala frågor i det samtid…</t>
+          <t>28 ord: - med högt ställda krav på skriftlig och muntlig kommunikationsförmåga, presente…</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>AKI2BN</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6480,23 +6480,23 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - analysera och formulera välgrundade perspektiv på centrala frågor i det samtid…</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI2BN</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>28 ord: - identifiera och förklara olika grammatiska svårigheter i det kinesiska språket…</t>
+          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för vanliga svårigheter svensktalande inlärare upplever gällande kine…</t>
+          <t>28 ord: - identifiera och förklara olika grammatiska svårigheter i det kinesiska språket…</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>26 ord: - redogöra för vanliga svårigheter svensktalande inlärare upplever gällande kine…</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>28 ord: - visa kunskap om bakgrunden till skolans styrdokument med fokus på det europeis…</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>28 ord: - visa kunskap om bakgrunden till skolans styrdokument med fokus på det europeis…</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>32 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
@@ -6800,7 +6800,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6810,23 +6810,23 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
@@ -6849,12 +6849,12 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>27 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr">
@@ -6866,7 +6866,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6876,63 +6876,63 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GPR256</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2018-10-10</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>28 ord: - inom given tidsram genomföra en självständig litteraturvetenskaplig eller språ…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GPR2VP</t>
+          <t>GPR256</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2022-03-04</t>
+          <t>2018-10-10</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -6953,19 +6953,19 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>26 ord: - kritiskt analysera och problematisera aktuella forskningsfrågor, begrepp, teor…</t>
+          <t>28 ord: - inom given tidsram genomföra en självständig litteraturvetenskaplig eller språ…</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR256</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GPR2XS</t>
+          <t>GPR2VP</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-03-04</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -6986,19 +6986,19 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>27 ord: - visa förståelse för olika aspekter av portugisiskans ljudsystem som betonings-…</t>
+          <t>26 ord: - kritiskt analysera och problematisera aktuella forskningsfrågor, begrepp, teor…</t>
         </is>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2VP</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GPR2XS</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -7019,19 +7019,19 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
+          <t>27 ord: - visa förståelse för olika aspekter av portugisiskans ljudsystem som betonings-…</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR2XS</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7047,24 +7047,24 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>PR1017</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7074,34 +7074,30 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2012-09-13</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>2016-04-14</t>
-        </is>
-      </c>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>28 ord: - visa insikt i det portugisiska språkets fonetik och fonologi genom att uttala …</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>PR1021</t>
+          <t>PR1017</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7111,7 +7107,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2014-09-11</t>
+          <t>2012-09-13</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -7126,32 +7122,36 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
+          <t>28 ord: - visa insikt i det portugisiska språkets fonetik och fonologi genom att uttala …</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1017</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GRY2BS</t>
+          <t>PR1021</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>2014-09-11</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2016-04-14</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7159,29 +7159,29 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>31 ord: - inom en given tidsram genomföra en självständig litteraturvetenskaplig, kultur…</t>
+          <t>27 ord: - reflektera över det portugisiska språkets geografiska spridning i världen och …</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=PR1021</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>GRY2BS</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2019-03-13</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -7192,19 +7192,19 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>31 ord: - inom en given tidsram genomföra en självständig litteraturvetenskaplig, kultur…</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2BS</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7214,27 +7214,23 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
+          <t>2019-03-13</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>33 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
@@ -7261,12 +7257,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>33 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
@@ -7303,7 +7299,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G204" s="2" t="inlineStr">
@@ -7340,7 +7336,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -7377,7 +7373,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="G206" s="2" t="inlineStr">
@@ -7414,7 +7410,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
@@ -7451,7 +7447,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
@@ -7488,7 +7484,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
@@ -7500,7 +7496,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7510,10 +7506,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7521,12 +7521,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7576,23 +7576,23 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>38 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
@@ -7615,12 +7615,12 @@
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>38 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>41 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7708,27 +7708,23 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 ord: - visa fördjupade kunskaper om användningen av digitala verktyg i språkundervisn…</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
@@ -7755,12 +7751,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>31 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
@@ -7772,7 +7768,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>GSP2YT</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7782,10 +7778,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -7793,19 +7793,19 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>GSP2YT</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -7826,19 +7826,19 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2YT</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7848,30 +7848,30 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -7892,19 +7892,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7914,40 +7914,40 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -7958,29 +7958,29 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -7991,29 +7991,29 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -8024,29 +8024,29 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -8057,217 +8057,217 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8277,30 +8277,30 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8310,30 +8310,30 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8343,30 +8343,30 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8376,30 +8376,30 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8409,30 +8409,30 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -8453,19 +8453,19 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -8486,19 +8486,19 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -8519,19 +8519,19 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -8552,19 +8552,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -8585,19 +8585,19 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -8618,19 +8618,19 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -8651,19 +8651,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -8684,19 +8684,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8706,30 +8706,30 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8739,30 +8739,34 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -8772,30 +8776,34 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -8805,30 +8813,30 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -8838,34 +8846,30 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -8875,34 +8879,34 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2016-11-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8912,34 +8916,30 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -8960,19 +8960,19 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -8982,30 +8982,30 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9015,40 +9015,40 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -9059,62 +9059,62 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -9125,29 +9125,29 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
+          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -9158,32 +9158,36 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
+          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -9191,32 +9195,36 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
+          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -9224,65 +9232,73 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
+          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2016-11-17</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -9295,24 +9311,24 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -9323,29 +9339,29 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
+          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -9356,19 +9372,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -9378,30 +9394,30 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9411,7 +9427,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -9422,19 +9438,19 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9444,7 +9460,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -9455,19 +9471,19 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9477,30 +9493,30 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9510,7 +9526,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -9521,19 +9537,19 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9543,7 +9559,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -9554,19 +9570,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>BSV22A</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9576,30 +9592,30 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - läsa, förstå och kritiskt värdera sakprosatexter i olika medier, med särskilt …</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BSV22A</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9609,30 +9625,30 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9642,30 +9658,30 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -9675,30 +9691,30 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -9708,7 +9724,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -9719,19 +9735,19 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
+          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9741,30 +9757,30 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9774,7 +9790,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -9785,19 +9801,19 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
+          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9807,7 +9823,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -9818,19 +9834,19 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9840,30 +9856,30 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9873,7 +9889,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -9884,19 +9900,19 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9906,30 +9922,30 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9945,24 +9961,24 @@
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -9983,19 +9999,19 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -10016,19 +10032,19 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10044,24 +10060,24 @@
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10071,7 +10087,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -10082,19 +10098,19 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
+          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -10104,7 +10120,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -10115,19 +10131,19 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -10137,7 +10153,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -10148,19 +10164,19 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
+          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -10170,7 +10186,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -10181,19 +10197,19 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
+          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -10203,7 +10219,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -10214,29 +10230,29 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
+          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -10247,95 +10263,95 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
+          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -10346,29 +10362,29 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -10379,29 +10395,29 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -10412,29 +10428,29 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -10445,62 +10461,62 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -10511,29 +10527,29 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -10544,29 +10560,29 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -10577,29 +10593,29 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3KH</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -10610,29 +10626,29 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - analysera och kritiskt granska betydelsen av ordförråd och språkförståelse i e…</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3KH</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -10643,29 +10659,29 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>29 ord: - analysera och bedöma elevers läsförmåga och diskutera hur bedömning av läsning…</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3KH</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -10676,29 +10692,29 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>30 ord: - analysera och bedöma elevers skrivförmåga och diskutera hur bedömning av skriv…</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GSV3KH</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -10709,19 +10725,19 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>27 ord: - problematisera och diskutera aspekter av läs- och skrivsvårigheter samt reflek…</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10742,19 +10758,19 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10764,30 +10780,30 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10797,30 +10813,30 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10830,7 +10846,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -10841,19 +10857,19 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10863,7 +10879,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -10874,19 +10890,19 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -10896,7 +10912,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -10907,19 +10923,19 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10929,7 +10945,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -10940,19 +10956,19 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10968,24 +10984,24 @@
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -11006,19 +11022,19 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -11028,30 +11044,30 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -11061,7 +11077,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -11072,19 +11088,19 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -11094,7 +11110,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -11105,19 +11121,19 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -11127,7 +11143,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -11138,19 +11154,19 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -11160,7 +11176,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -11171,19 +11187,19 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -11193,7 +11209,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -11204,19 +11220,19 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -11226,7 +11242,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -11237,19 +11253,19 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -11259,30 +11275,30 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -11292,30 +11308,30 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -11325,14 +11341,10 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11340,19 +11352,19 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -11362,14 +11374,10 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11382,14 +11390,14 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -11399,14 +11407,10 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11414,19 +11418,19 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -11436,7 +11440,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -11447,19 +11451,19 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -11469,7 +11473,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -11480,19 +11484,19 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -11502,7 +11506,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -11513,19 +11517,19 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11535,34 +11539,30 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11572,14 +11572,10 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11587,19 +11583,19 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -11609,14 +11605,10 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11624,19 +11616,19 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11646,14 +11638,10 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11661,19 +11649,19 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11683,14 +11671,10 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11698,19 +11682,19 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11720,14 +11704,10 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11735,19 +11715,19 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -11757,14 +11737,10 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -11772,19 +11748,19 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -11794,69 +11770,901 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>38 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>GTY3KG</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>TY1069</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>TY1071</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2016-11-01</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>TY1073</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>TY3013</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C363" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
         <is>
           <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
         </is>
       </c>
-      <c r="G339" s="2" t="inlineStr">
+      <c r="G363" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G339"/>
+  <autoFilter ref="A1:G363"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -12534,6 +13342,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G338" r:id="rId674"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A339" r:id="rId675"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G339" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A340" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G340" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A341" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G341" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A342" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G342" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A343" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G343" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A344" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G344" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A345" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G345" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A346" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G346" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A347" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G347" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A348" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G348" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A349" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G349" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A350" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G350" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A351" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G351" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A352" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G352" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A353" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G353" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A354" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G354" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A355" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G355" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A356" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G356" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A357" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G357" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A358" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G358" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A359" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G359" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A360" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G360" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A361" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G361" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A362" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A363" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId724"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Omfång på lärandemål.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Omfång på lärandemål" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$363</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Omfång på lärandemål'!$A$1:$G$364</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G363"/>
+  <dimension ref="A1:G364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7838,7 +7838,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>GSP3KS</t>
+          <t>GSP3GW</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7848,23 +7848,23 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - inom givna tidsramar genomföra en självständig språkvetenskaplig studie med kr…</t>
         </is>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3GW</t>
         </is>
       </c>
     </row>
@@ -7887,12 +7887,12 @@
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G221" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>33 ord: - visa förtrogenhet med uppbyggnaden av vetenskapliga texter, vilket innefattar …</t>
         </is>
       </c>
       <c r="G222" s="2" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G223" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
+          <t>36 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
+          <t>29 ord: - visa förmåga att självständigt välja relevant innehåll och arbetssätt i språku…</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
+          <t>29 ord: - visa fördjupade kunskaper om den gemensamma europeiska referensramen för språk…</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
+          <t>30 ord: - visa fördjupade kunskaper om användningen av IKT i språkundervisningen, IKT-ut…</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -8156,19 +8156,19 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
+          <t>30 ord: - visa förmåga att ställa en relevant forskningsfråga inom ett avgränsat problem…</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8189,19 +8189,19 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
+          <t>28 ord: - inom givna tidsramar genomföra en självständig litteraturvetenskaplig studie m…</t>
         </is>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8227,14 +8227,14 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>SP2024</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8250,57 +8250,57 @@
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>För få mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
+          <t>27 ord: - reflektera över, värdera och kritiskt granska vetenskapliga artiklar och textt…</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ASS257</t>
+          <t>SP2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För få mål</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>3 lärandemål (minimum rekommenderat: 4 för 15 hp)</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2024</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>ASS258</t>
+          <t>ASS257</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS257</t>
         </is>
       </c>
     </row>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>36 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -8366,7 +8366,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ASS28X</t>
+          <t>ASS258</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -8387,19 +8387,19 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS258</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>ASS28X</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8409,30 +8409,30 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - inom givna ramar genomföra en självständig studie med krav på vetenskapligt vä…</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASS28X</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -8453,19 +8453,19 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -8491,14 +8491,14 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -8519,19 +8519,19 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -8552,19 +8552,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>32 lärandemål (maximum rekommenderat: 15 för 67.5 hp)</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -8585,19 +8585,19 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -8618,19 +8618,19 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>24 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
@@ -8651,19 +8651,19 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>19 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -8684,19 +8684,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
+          <t>13 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -8717,19 +8717,19 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>53 lärandemål (maximum rekommenderat: 15 för 90 hp)</t>
         </is>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8739,34 +8739,30 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
+          <t>21 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -8786,24 +8782,24 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - analysera och kritiskt granska vetenskapliga texter inom för kursen relevant ä…</t>
         </is>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -8813,10 +8809,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr"/>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -8824,19 +8824,19 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -8857,19 +8857,19 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -8879,14 +8879,10 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -8894,19 +8890,19 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8916,10 +8912,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr"/>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>För många mål</t>
@@ -8927,19 +8927,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
@@ -8965,14 +8965,14 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -8993,19 +8993,19 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -9026,19 +9026,19 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>16 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>GSS3K2</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9048,30 +9048,30 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3K2</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -9081,23 +9081,23 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
+          <t>26 ord: - reflektera över egen och andras undervisningsplanering med skönlitteratur i sk…</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3K2</t>
         </is>
       </c>
     </row>
@@ -9120,12 +9120,12 @@
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
+          <t>26 lärandemål (maximum rekommenderat: 15 för 45 hp)</t>
         </is>
       </c>
       <c r="G258" s="2" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
+          <t>30 ord: - visa insikt i att uttalet förutom att signalera ett visst förstaspråk även kan…</t>
         </is>
       </c>
       <c r="G259" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>SS2007</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9180,14 +9180,10 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>2016-11-17</t>
-        </is>
-      </c>
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -9195,12 +9191,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
+          <t>26 ord: - planera undervisning för att främja elevernas utveckling av strategier för läs…</t>
         </is>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9228,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
+          <t>26 ord: - visa förmåga att utifrån en väl avgränsad problemställning självständigt söka,…</t>
         </is>
       </c>
       <c r="G261" s="2" t="inlineStr">
@@ -9269,7 +9265,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
+          <t>30 ord: - inom givna tidsramar genomföra en självständig studie med krav på vetenskaplig…</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -9281,7 +9277,7 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS2007</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -9296,29 +9292,29 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2016-11-17</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>29 ord: - självständigt och kritiskt analysera och diskutera andras examensarbeten utifr…</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2007</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>SS3011</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -9328,23 +9324,27 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2016-06-09</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
+          <t>28 ord: - visa god förmåga att tillämpa kunskap om andraspråksforskningen generellt samt…</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>SS3011</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2016-06-09</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -9405,19 +9405,19 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
+          <t>28 ord: - visa fördjupad förmåga att analysera, värdera och diskutera andras vetenskapli…</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS3011</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9443,14 +9443,14 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>ASV2CP</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -9471,12 +9471,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
+          <t>26 ord: - visa fördjupad förmåga att i tal och skrift beskriva och argumentera för den e…</t>
         </is>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
+          <t>28 ord: - analysera och värdera sambandet mellan elevers språkförståelse, läsförkunskape…</t>
         </is>
       </c>
       <c r="G269" s="2" t="inlineStr">
@@ -9516,7 +9516,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>ASV2CQ</t>
+          <t>ASV2CP</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
+          <t>27 ord: - problematisera och diskutera utmaningar i undervisningen i förskoleklass och å…</t>
         </is>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CP</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
+          <t>30 ord: - analysera och värdera sambandet mellan elevers språkförståelse, fortsatta läsu…</t>
         </is>
       </c>
       <c r="G271" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>BSV22A</t>
+          <t>ASV2CQ</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -9603,19 +9603,19 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>26 ord: - läsa, förstå och kritiskt värdera sakprosatexter i olika medier, med särskilt …</t>
+          <t>29 ord: - analysera och kritiskt granska hur läsundervisningen kan stödja utvecklingen a…</t>
         </is>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BSV22A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2CQ</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>BSV22A</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9625,30 +9625,30 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - läsa, förstå och kritiskt värdera sakprosatexter i olika medier, med särskilt …</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BSV22A</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
@@ -9697,12 +9697,12 @@
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
+          <t>23 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
+          <t>26 ord: - redogöra för olika sätt att betrakta språk och för vilken betydelse olika språ…</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9763,17 +9763,17 @@
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>26 ord: - visa kunskap om skönlitterära genrer och litteraturvetenskapliga begrepp samt …</t>
         </is>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
@@ -9796,12 +9796,12 @@
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>30 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="G279" s="2" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9862,17 +9862,17 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
@@ -9895,12 +9895,12 @@
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
+          <t>25 lärandemål (maximum rekommenderat: 10 för 15 hp)</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
+          <t>28 ord: - med grund i läst avhandling skriftligt analysera och jämföra olika teorier om …</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -9945,7 +9945,7 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9955,23 +9955,23 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>31 ord: - analysera och bedöma elevers skrivförmåga utifrån autentiska texter och visa f…</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
@@ -9994,12 +9994,12 @@
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
+          <t>20 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - reflektera över texter och andra verktyg som medel för att stimulera elevers s…</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -10044,7 +10044,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G287" s="2" t="inlineStr">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>27 ord: - göra kritiska läsningar av skönlitterära verk och diskutera deras potential so…</t>
         </is>
       </c>
       <c r="G288" s="2" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
+          <t>32 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
+          <t>28 ord: - beskriva olika typer av språkpolicy samt utifrån exempel från Sverige och Nord…</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
+          <t>33 ord: - föra en fördjupad diskussion kring hur ungdomars utveckling av litteracitet oc…</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - utifrån aktuell forskning och beprövad erfarenhet planera svenskundervisning s…</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
@@ -10275,7 +10275,7 @@
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -10291,17 +10291,17 @@
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>41 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>23 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>49 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
+          <t>45 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G296" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
+          <t>28 ord: - utifrån sina samlade kunskaper om litteraturvetenskap, språkvetenskap och ämne…</t>
         </is>
       </c>
       <c r="G297" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>GSV3FP</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -10461,12 +10461,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
+          <t>36 ord: - tala och skriva i enlighet med de normer som finns för formell svenska och på …</t>
         </is>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
+          <t>35 ord: - förklara samt redogöra för betydelsen av ordförråd och språkförståelse i eleve…</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3FP</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="D300" t="inlineStr"/>
@@ -10527,12 +10527,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
+          <t>27 ord: - beskriva och problematisera särskilda utmaningar i läs- och skrivinlärning och…</t>
         </is>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3FP</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
+          <t>31 ord: - redogöra för, välja och tillämpa olika metoder och material i läs- och skrivun…</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
+          <t>31 ord: - reflektera över barns bruk av skrift och andra medier i och utanför skolan sam…</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>GSV3KH</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -10626,12 +10626,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>35 ord: - analysera och kritiskt granska betydelsen av ordförråd och språkförståelse i e…</t>
+          <t>26 ord: - självständigt tala och skriva i enlighet med de normer som finns för formell s…</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>29 ord: - analysera och bedöma elevers läsförmåga och diskutera hur bedömning av läsning…</t>
+          <t>35 ord: - analysera och kritiskt granska betydelsen av ordförråd och språkförståelse i e…</t>
         </is>
       </c>
       <c r="G304" s="2" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>30 ord: - analysera och bedöma elevers skrivförmåga och diskutera hur bedömning av skriv…</t>
+          <t>29 ord: - analysera och bedöma elevers läsförmåga och diskutera hur bedömning av läsning…</t>
         </is>
       </c>
       <c r="G305" s="2" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>27 ord: - problematisera och diskutera aspekter av läs- och skrivsvårigheter samt reflek…</t>
+          <t>30 ord: - analysera och bedöma elevers skrivförmåga och diskutera hur bedömning av skriv…</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
@@ -10737,17 +10737,17 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>ATY2B7</t>
+          <t>GSV3KH</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -10758,19 +10758,19 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
+          <t>27 ord: - problematisera och diskutera aspekter av läs- och skrivsvårigheter samt reflek…</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>GTY2N3</t>
+          <t>ATY2B7</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -10791,19 +10791,19 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>29 ord: - muntligt och skriftligt analysera, värdera och kritiskt granska egna och andra…</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B7</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY2N3</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10819,17 +10819,17 @@
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N3</t>
         </is>
       </c>
     </row>
@@ -10852,12 +10852,12 @@
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
+          <t>22 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
@@ -10869,7 +10869,7 @@
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>GTY32H</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -10890,12 +10890,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>30 ord: - sammanställa en korpus genom ett urval av digital text som producerats i en in…</t>
         </is>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G312" s="2" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G313" s="2" t="inlineStr">
@@ -10968,7 +10968,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY32H</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10978,23 +10978,23 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-01-27</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>35 ord: - visa kunskap om olika former av digitala verktyg och hur de kan användas i spr…</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY32H</t>
         </is>
       </c>
     </row>
@@ -11017,12 +11017,12 @@
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+          <t>36 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G318" s="2" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G319" s="2" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G320" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
@@ -11265,7 +11265,7 @@
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -11281,17 +11281,17 @@
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
@@ -11314,12 +11314,12 @@
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>34 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G328" s="2" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G329" s="2" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G330" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11539,23 +11539,23 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
@@ -11578,12 +11578,12 @@
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>37 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G337" s="2" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
@@ -11793,7 +11793,7 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -11809,24 +11809,24 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>GTY3KG</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -11847,12 +11847,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>38 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
+          <t>15 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
@@ -11875,12 +11875,12 @@
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Långt mål</t>
+          <t>För många mål</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
+          <t>38 lärandemål (maximum rekommenderat: 12 för 30 hp)</t>
         </is>
       </c>
       <c r="G341" s="2" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
+          <t>30 ord: - genomföra och ge respons på kortare muntliga och skriftliga presentationer av …</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
+          <t>26 ord: - med utgångspunkt i elevers kunskapsbehov och individuella förutsättningar för …</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
@@ -11979,7 +11979,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>33 ord: - reflektera över elevers syn på och upplevelser av sitt språklärande samt disku…</t>
         </is>
       </c>
       <c r="G344" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G345" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
+          <t>35 ord: - redogöra för olika former av digitala verktyg och diskutera hur de kan använda…</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
+          <t>28 ord: - självständigt välja relevanta innehåll och arbetssätt i planeringen av språkun…</t>
         </is>
       </c>
       <c r="G347" s="2" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
+          <t>33 ord: - redogöra för hur digitala verktyg kan användas i språkundervisningen, redogöra…</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
@@ -12123,7 +12123,7 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3KG</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -12133,14 +12133,10 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -12148,12 +12144,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
+          <t>26 ord: - ställa en relevant forskningsfråga inom ett avgränsat problemområde som är kop…</t>
         </is>
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
         </is>
       </c>
     </row>
@@ -12185,7 +12181,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
+          <t>35 ord: - visa kunskap om elevers syn på och upplevelser av sitt språklärande samt refle…</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
@@ -12222,7 +12218,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
+          <t>35 ord: - diskutera och reflektera över samspelet mellan inre och yttre faktorer som är …</t>
         </is>
       </c>
       <c r="G351" s="2" t="inlineStr">
@@ -12234,7 +12230,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -12244,10 +12240,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr"/>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -12255,19 +12255,19 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
+          <t>27 ord: - visa kunskap om olika former av informations- och kommunikationsteknik och hur…</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>TY1071</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2016-11-01</t>
+          <t>2016-02-11</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -12288,19 +12288,19 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
+          <t>28 ord: - visa ett självständigt och kritiskt förhållningssätt till olika metoder inom ä…</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>TY1071</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
@@ -12321,19 +12321,19 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
+          <t>29 ord: - visa kunskaper i det tyska språkets uppbyggnad och tillämpa dessa i muntliga o…</t>
         </is>
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1071</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -12343,14 +12343,10 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
           <t>Långt mål</t>
@@ -12358,12 +12354,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
+          <t>26 ord: - göra bedömningar baserade på kunskap rörande relevanta samhällsetiska frågor s…</t>
         </is>
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12391,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
+          <t>45 ord: - ha samlat kunskaper om några utvalda aktuella forskningsfrågor samt genom förf…</t>
         </is>
       </c>
       <c r="G356" s="2" t="inlineStr">
@@ -12432,7 +12428,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>50 ord: - medvetet kunna använda en omfattande praktisk och teoretisk kunskap inom antin…</t>
         </is>
       </c>
       <c r="G357" s="2" t="inlineStr">
@@ -12469,7 +12465,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="G358" s="2" t="inlineStr">
@@ -12481,7 +12477,7 @@
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -12506,12 +12502,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
+          <t>33 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant identifiera eventuella yt…</t>
         </is>
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12539,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
+          <t>44 ord: - kunna använda en omfattande praktisk och teoretisk kunskap inom tysk språkvete…</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
@@ -12580,7 +12576,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
+          <t>27 ord: - visa prov på hög grad av självständighet och problemlösningsförmåga i umgänget…</t>
         </is>
       </c>
       <c r="G361" s="2" t="inlineStr">
@@ -12592,7 +12588,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -12602,69 +12598,106 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>För många mål</t>
+          <t>Långt mål</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+          <t>34 ord: - kritiskt kunna utvärdera det egna lärandet, noggrant kunna identifiera eventue…</t>
         </is>
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
+          <t>TY3013</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>För många mål</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>9 lärandemål (maximum rekommenderat: 8 för 7.5 hp)</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
+      <c r="C364" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="D364" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>Långt mål</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Långt mål</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
         <is>
           <t>26 ord: - uttrycka sig skriftligt och muntligt på tyska med mycket stor språklig säkerhe…</t>
         </is>
       </c>
-      <c r="G363" s="2" t="inlineStr">
+      <c r="G364" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G363"/>
+  <autoFilter ref="A1:G364"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -13390,6 +13423,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId722"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A363" r:id="rId723"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A364" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId726"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
